--- a/data/reason_code_library_2.xlsx
+++ b/data/reason_code_library_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tergel.mu\Downloads\user-score-v1.1\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B265AAD-D883-4D81-AA1C-0C741FDF9452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D07C679-5DA5-46F6-B35E-2C3E59CC722C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1993" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="383">
   <si>
     <t>model_group</t>
   </si>
@@ -11686,17 +11686,11 @@
         <v>78.430000000000007</v>
       </c>
       <c r="G364" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H364" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="I364" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J364" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H364" s="3"/>
+      <c r="I364" s="3"/>
+      <c r="J364" s="3"/>
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
@@ -11718,17 +11712,11 @@
         <v>17.14</v>
       </c>
       <c r="G365" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H365" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I365" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J365" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H365" s="3"/>
+      <c r="I365" s="3"/>
+      <c r="J365" s="3"/>
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
@@ -11750,17 +11738,11 @@
         <v>4.43</v>
       </c>
       <c r="G366" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H366" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I366" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J366" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H366" s="3"/>
+      <c r="I366" s="3"/>
+      <c r="J366" s="3"/>
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
